--- a/framework-pdfs/PFWP Action Log.xlsx
+++ b/framework-pdfs/PFWP Action Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Martin/Documents/0 Punkfrog/06 Quality/Templates/02 Planning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6A6FF7-BC44-9B4B-AB71-68DC22BD0573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21162C2-850C-384E-BDF4-AEEE8AD07900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16100" yWindow="-25600" windowWidth="23660" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2508,7 +2508,7 @@
   </si>
   <si>
     <t>PF/P-26:001
-2026-03-06 version 1.0.1</t>
+2026-03-06 version 2.0.0</t>
   </si>
 </sst>
 </file>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="B1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>16</v>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="B1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>16</v>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="C1" s="2">
         <f ca="1">NOW()</f>
-        <v>46087.951647222224</v>
+        <v>46090.715854861111</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
@@ -34448,7 +34448,7 @@
       </c>
       <c r="C1" s="2">
         <f ca="1">NOW()</f>
-        <v>46087.951647222224</v>
+        <v>46090.715854861111</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
@@ -41371,7 +41371,7 @@
       </c>
       <c r="B1" s="2">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>16</v>
@@ -45807,7 +45807,7 @@
       </c>
       <c r="B5" s="48">
         <f ca="1">TODAY()</f>
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>255</v>
@@ -48706,7 +48706,7 @@
       </c>
       <c r="B1" s="2">
         <f ca="1">NOW()</f>
-        <v>46087.951647222224</v>
+        <v>46090.715854861111</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>16</v>
